--- a/assets/constructions/examples/ctd_tmfi_holder.xlsx
+++ b/assets/constructions/examples/ctd_tmfi_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,21 +614,41 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GVIL32-29</t>
+          <t>A10SNEL2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GVN</t>
+          <t>A-NNT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,28 +663,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VAR_GVI_29</t>
+          <t>WID_N02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N.2R</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ISO_5609:32</t>
+          <t>ISO_5609:15.875</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>VARGUS_GVN:29L</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>WIDIA_N02</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>25.4</v>
+      </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>15.875</v>
       </c>
       <c r="M2" t="n">
         <v>90</v>
@@ -678,17 +704,15 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="b">
         <v>0</v>
@@ -697,30 +721,26 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>22.2</v>
+        <v>12.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>19</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
@@ -736,24 +756,30 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2020 / WIDIA Turning Catalogue</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVR50-5V</t>
+          <t>A40TNNTOR3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>V-Style</t>
+          <t>A-NNT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -763,53 +789,59 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VAR_IC5/8V</t>
+          <t>WID_N03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N.3L</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ISO_5609:50</t>
+          <t>ISO_5609:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VARGUS_5/8VIR</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>WIDIA_N03</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>54</v>
+      </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -834,45 +866,51 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>33.4</v>
+        <v>27</v>
       </c>
       <c r="AD3" t="n">
-        <v>350</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>200</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="b">
+        <v>0</v>
+      </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2018/VARGUS Catalog VARDEX</t>
-        </is>
-      </c>
+          <t>2020 / WIDIA Turning Catalogue</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A12SNER2</t>
+          <t>NVR50-5VLH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A-NNT</t>
+          <t>V-Style</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -882,59 +920,53 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WID_N02</t>
+          <t>VAR_IC5/8V</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>N.2L</t>
-        </is>
-      </c>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ISO_5609:19.05</t>
+          <t>ISO_5609:50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WIDIA_N02</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>28.575</v>
-      </c>
+          <t>VARGUS_5/8VIL</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>19.05</v>
+        <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -959,29 +991,43 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>14.275</v>
+        <v>33.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>254</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>200</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="AH4" t="b">
-        <v>0</v>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Turning Catalogue</t>
-        </is>
+          <t>2018/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>31836.64</v>
       </c>
     </row>
     <row r="5">
@@ -992,7 +1038,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A40TNNTOL3</t>
+          <t>A25RNNTOL2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1012,7 +1058,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WID_N03</t>
+          <t>WID_N02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,24 +1068,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>N.3R</t>
+          <t>N.2R</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ISO_5609:40</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WIDIA_N03</t>
+          <t>WIDIA_N02</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M5" t="n">
         <v>90</v>
@@ -1084,10 +1130,10 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AD5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1108,21 +1154,27 @@
           <t>2020 / WIDIA Turning Catalogue</t>
         </is>
       </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A32NER3</t>
+          <t>NVRC60-5VLH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A-NNT</t>
+          <t>V-Style</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1132,59 +1184,53 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WID_N03</t>
+          <t>VAR_IC5/8V</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>N.3L</t>
-        </is>
-      </c>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISO_5609:50.8</t>
+          <t>ISO_5609:60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WIDIA_N03</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>63.5</v>
-      </c>
+          <t>VARGUS_5/8VIL</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>50.8</v>
+        <v>60</v>
       </c>
       <c r="M6" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1195,10 +1241,10 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1209,29 +1255,43 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>31.75</v>
+        <v>38</v>
       </c>
       <c r="AD6" t="n">
-        <v>406.4</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>240</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="AH6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Turning Catalogue</t>
-        </is>
+          <t>2018/VARGUS Catalog VARDEX</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>475.68</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>43731.02</v>
       </c>
     </row>
   </sheetData>
